--- a/StructureDefinition-follow-up-appointment-profile.xlsx
+++ b/StructureDefinition-follow-up-appointment-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-follow-up-appointment-profile.xlsx
+++ b/StructureDefinition-follow-up-appointment-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-follow-up-appointment-profile.xlsx
+++ b/StructureDefinition-follow-up-appointment-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
